--- a/datos_de_prueba/Matriz de prueba - 110 oficios.xlsx
+++ b/datos_de_prueba/Matriz de prueba - 110 oficios.xlsx
@@ -595,7 +595,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1836,7 +1836,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2288,7 +2288,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3077,7 +3077,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3300,7 +3300,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3408,7 +3408,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4193,7 +4193,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4304,7 +4304,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4419,7 +4419,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4649,7 +4649,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4875,7 +4875,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4986,7 +4986,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5097,7 +5097,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5212,7 +5212,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5442,7 +5442,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5557,7 +5557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5672,7 +5672,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5902,7 +5902,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6239,7 +6239,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6461,7 +6461,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6687,7 +6687,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6798,7 +6798,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6913,7 +6913,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7143,7 +7143,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7254,7 +7254,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7480,7 +7480,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7706,7 +7706,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8029,7 +8029,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8248,7 +8248,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8363,7 +8363,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8593,7 +8593,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8708,7 +8708,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8812,7 +8812,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9244,7 +9244,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9360,7 +9360,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9480,7 +9480,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9720,7 +9720,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9840,7 +9840,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9956,7 +9956,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10308,7 +10308,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10428,7 +10428,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10544,7 +10544,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10660,7 +10660,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10775,7 +10775,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11015,7 +11015,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11135,7 +11135,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11250,7 +11250,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11365,7 +11365,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -11480,7 +11480,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11591,7 +11591,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11702,7 +11702,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11928,7 +11928,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -12039,7 +12039,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12154,7 +12154,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12265,7 +12265,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12501,7 +12501,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12616,7 +12616,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12727,7 +12727,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12957,7 +12957,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -13068,7 +13068,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -13179,7 +13179,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -13405,7 +13405,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -13516,7 +13516,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -13620,7 +13620,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13740,7 +13740,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13855,7 +13855,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13970,7 +13970,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -14085,7 +14085,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -14200,7 +14200,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -14315,7 +14315,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -14430,7 +14430,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -14545,7 +14545,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -14656,7 +14656,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -14771,7 +14771,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -14886,7 +14886,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -15002,7 +15002,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -15118,7 +15118,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -15234,7 +15234,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -15354,7 +15354,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -15470,7 +15470,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -15590,7 +15590,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -15706,7 +15706,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -15822,7 +15822,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -15938,7 +15938,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -16170,7 +16170,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -16406,7 +16406,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -16526,7 +16526,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -16642,7 +16642,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -16762,7 +16762,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -16878,7 +16878,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -16994,7 +16994,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -17226,7 +17226,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -17346,7 +17346,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -17578,7 +17578,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -17814,7 +17814,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -17934,7 +17934,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -18166,7 +18166,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -18286,7 +18286,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -18406,7 +18406,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -18526,7 +18526,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -18646,7 +18646,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -18762,7 +18762,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -18878,7 +18878,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -18994,7 +18994,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -19110,7 +19110,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -19342,7 +19342,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -19458,7 +19458,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -19578,7 +19578,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -19686,7 +19686,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -19790,7 +19790,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -20018,7 +20018,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -20134,7 +20134,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -20250,7 +20250,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -20366,7 +20366,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -20606,7 +20606,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -20726,7 +20726,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -20846,7 +20846,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -20966,7 +20966,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -21082,7 +21082,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -21202,7 +21202,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -21322,7 +21322,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -21438,7 +21438,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -21558,7 +21558,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -21770,7 +21770,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -21890,7 +21890,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -22006,7 +22006,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -22126,7 +22126,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -22246,7 +22246,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -22366,7 +22366,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -22486,7 +22486,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -22606,7 +22606,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -22726,7 +22726,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -22842,7 +22842,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -22958,7 +22958,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -23078,7 +23078,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -23198,7 +23198,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -23314,7 +23314,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -23434,7 +23434,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -23554,7 +23554,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -23674,7 +23674,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -23790,7 +23790,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -23906,7 +23906,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -24022,7 +24022,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -24142,7 +24142,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -24258,7 +24258,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -24378,7 +24378,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -24494,7 +24494,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -24610,7 +24610,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -24730,7 +24730,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -24846,7 +24846,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -24962,7 +24962,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -25082,7 +25082,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -25198,7 +25198,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -25314,7 +25314,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -25430,7 +25430,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -25550,7 +25550,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -25670,7 +25670,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -25786,7 +25786,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -25902,7 +25902,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -26022,7 +26022,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -26138,7 +26138,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -26258,7 +26258,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -26378,7 +26378,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -26494,7 +26494,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -26614,7 +26614,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -26730,7 +26730,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -26846,7 +26846,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -26966,7 +26966,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -27082,7 +27082,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -27202,7 +27202,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -27322,7 +27322,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -27442,7 +27442,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -27558,7 +27558,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -27678,7 +27678,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -27914,7 +27914,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -28034,7 +28034,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -28154,7 +28154,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -28270,7 +28270,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -28390,7 +28390,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -28506,7 +28506,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -28626,7 +28626,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -28746,7 +28746,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -28866,7 +28866,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -28986,7 +28986,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -29106,7 +29106,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
